--- a/results/Int All Data -0.1/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_10_permute.xlsx
@@ -440,187 +440,187 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.855147108759007</v>
+        <v>0.8495770740056514</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8532411367132637</v>
+        <v>0.8527059586601404</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8545117847437592</v>
+        <v>0.8513351646675203</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8390159810318134</v>
+        <v>0.8535893100213874</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8563872454890027</v>
+        <v>0.8520009999832679</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.849137366796028</v>
+        <v>0.8527755933217653</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8487109467656545</v>
+        <v>0.8498470005915255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8508954574578969</v>
+        <v>0.8550297386756324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8501904987810243</v>
+        <v>0.8487547452454043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8472705181114095</v>
+        <v>0.8475232205760337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8449772493964176</v>
+        <v>0.8468878965607859</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8449772493964176</v>
+        <v>0.8475232205760337</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8443419253811698</v>
+        <v>0.8443466004997948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8435978433431723</v>
+        <v>0.8426190211384259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8414133326509301</v>
+        <v>0.8396207937465613</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8458911120581644</v>
+        <v>0.840573779769433</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8458911120581644</v>
+        <v>0.8412787384463055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8458519886970395</v>
+        <v>0.8492507999374026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8445117060049192</v>
+        <v>0.8447338971690435</v>
       </c>
     </row>
     <row r="21">
@@ -630,527 +630,527 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8458128653359147</v>
+        <v>0.8446251391462938</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8458824999975394</v>
+        <v>0.8432371210324237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8458824999975394</v>
+        <v>0.8307090334118425</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8458128653359147</v>
+        <v>0.8295471434040966</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8460608926819138</v>
+        <v>0.8295471434040966</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8457823540354148</v>
+        <v>0.8297560473889709</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8408867666584319</v>
+        <v>0.8371013969254452</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8369050419431958</v>
+        <v>0.838307085412941</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8407780086356823</v>
+        <v>0.8420493948428028</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8407780086356823</v>
+        <v>0.8436682161814222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8375622651983186</v>
+        <v>0.8525322410943912</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.831705079737839</v>
+        <v>0.8536244964405123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8283891903383507</v>
+        <v>0.8498477387681505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8238026529083666</v>
+        <v>0.8503743047606487</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8235546255623676</v>
+        <v>0.8498782500686504</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8252908169843615</v>
+        <v>0.8498782500686504</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8255998669313604</v>
+        <v>0.8495605880610266</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8226321508399957</v>
+        <v>0.8505135740838983</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8226321508399957</v>
+        <v>0.8578503115597476</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8233457215774933</v>
+        <v>0.8484159221745305</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8233457215774933</v>
+        <v>0.8479808900835322</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8119709119040331</v>
+        <v>0.8163438702305178</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.811722884558034</v>
+        <v>0.815995696922394</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8079586758882971</v>
+        <v>0.8098818720552904</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8111744193256609</v>
+        <v>0.8149472400560227</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7826928584856356</v>
+        <v>0.8144903087251493</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7788198917931491</v>
+        <v>0.8114443459115349</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7724533644614214</v>
+        <v>0.8277804406816027</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7776971251465281</v>
+        <v>0.8337072608037071</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7487382100890044</v>
+        <v>0.826278989426358</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7469151598841358</v>
+        <v>0.826278989426358</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.757737567383223</v>
+        <v>0.8279369341261023</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7491779172986279</v>
+        <v>0.8247470268706134</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7508186378771222</v>
+        <v>0.818864005228259</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7517716238999939</v>
+        <v>0.8052515361455567</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.745409771686891</v>
+        <v>0.8132760081770285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7456664110935152</v>
+        <v>0.7925996809108509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.725157649921212</v>
+        <v>0.7878910982788674</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7380777093296667</v>
+        <v>0.7839398848641312</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7178693860437375</v>
+        <v>0.7645930136995739</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7130739446288792</v>
+        <v>0.7686224738365599</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7171166919451151</v>
+        <v>0.7470340063207603</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7262897668050829</v>
+        <v>0.7470340063207603</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7371599097259199</v>
+        <v>0.7423692221685267</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7381128957487916</v>
+        <v>0.7428261534994001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7375080830340437</v>
+        <v>0.74715211458076</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7351756909579269</v>
+        <v>0.7199552271271051</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7340834356118058</v>
+        <v>0.7197290990209809</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7328127875813102</v>
+        <v>0.7199771263669801</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7328127875813102</v>
+        <v>0.6938592070801965</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.735145179657427</v>
+        <v>0.6992289499093027</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7347578829881783</v>
+        <v>0.718862971780984</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6945368532219441</v>
+        <v>0.7184803502303603</v>
       </c>
     </row>
     <row r="74">
@@ -1160,827 +1160,827 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7027702292382902</v>
+        <v>0.6881240668217166</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7092541266533926</v>
+        <v>0.6490649270632283</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.706286410562028</v>
+        <v>0.6494522237324769</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6903250634585838</v>
+        <v>0.6501266711088496</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6776271952142534</v>
+        <v>0.6485164618308552</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6796333132221213</v>
+        <v>0.6255102030773108</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6647947327652982</v>
+        <v>0.6238522583775665</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6523535039275918</v>
+        <v>0.6038309398366366</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6468225925353611</v>
+        <v>0.6007239544220224</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6468225925353611</v>
+        <v>0.5833049545430834</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6462569031817381</v>
+        <v>0.5519565617504432</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6481323639269816</v>
+        <v>0.5513689731569452</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6409395708930068</v>
+        <v>0.5519479496898182</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6336638560181571</v>
+        <v>0.5716821175236241</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6500954216317246</v>
+        <v>0.571999779531248</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.658872587761819</v>
+        <v>0.5501507356668245</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6591902497694428</v>
+        <v>0.5520348084726928</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6602825051155641</v>
+        <v>0.5526004978263159</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6609960758530615</v>
+        <v>0.5549547891423077</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6585244144536951</v>
+        <v>0.5389151953166138</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6550387444304574</v>
+        <v>0.5147642706765733</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6552171371148318</v>
+        <v>0.510277879208714</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.64998198849035</v>
+        <v>0.5093554044863422</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6510828558970962</v>
+        <v>0.5068923551476009</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6651992535557968</v>
+        <v>0.5056608304782302</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.690551191564708</v>
+        <v>0.5056608304782302</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6926269442342008</v>
+        <v>0.504855725839233</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6980271983638069</v>
+        <v>0.504855725839233</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.712857166760005</v>
+        <v>0.5045380638316092</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7133140980908783</v>
+        <v>0.5047860911776082</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7176831194753631</v>
+        <v>0.4945035368502692</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7147545267451234</v>
+        <v>0.4918534827665285</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7147545267451234</v>
+        <v>0.4958743308428895</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5845059679119542</v>
+        <v>0.4949909794816425</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5808332931437171</v>
+        <v>0.4943556554663948</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5844363332503295</v>
+        <v>0.4943556554663948</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5876129533265684</v>
+        <v>0.4970667321511353</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5589060025570438</v>
+        <v>0.4951693721660169</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5411083180694811</v>
+        <v>0.496857828166261</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5411302173093561</v>
+        <v>0.5015272874371197</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.556277847713178</v>
+        <v>0.5015272874371197</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5568740483673009</v>
+        <v>0.5015272874371197</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5594849790899168</v>
+        <v>0.5015969220987444</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5594849790899168</v>
+        <v>0.5036726747682372</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5611124124891611</v>
+        <v>0.5036726747682372</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5455993846559654</v>
+        <v>0.5036726747682372</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5388893591347389</v>
+        <v>0.5067796601828513</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5335587396667576</v>
+        <v>0.5062139708292283</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5187592825710593</v>
+        <v>0.5065316328368521</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.521161309308801</v>
+        <v>0.504556026129484</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5365960904197469</v>
+        <v>0.5026500540837407</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5467174761839615</v>
+        <v>0.5026500540837407</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5607814633022873</v>
+        <v>0.50144904071487</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5618651065877834</v>
+        <v>0.501131378707246</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5526137850055659</v>
+        <v>0.501131378707246</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5458341248227145</v>
+        <v>0.5019059720457433</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5455164628150907</v>
+        <v>0.5007440820379974</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5288196457342741</v>
+        <v>0.5007440820379974</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5263393722742828</v>
+        <v>0.5010617440456213</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5221315194529226</v>
+        <v>0.5010617440456213</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5085940983270949</v>
+        <v>0.500883351361247</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5029153055509897</v>
+        <v>0.5013488947527452</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5032329675586137</v>
+        <v>0.5020538534296178</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5032329675586137</v>
+        <v>0.5033550127606132</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5010007214446215</v>
+        <v>0.5018754607452434</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5026586661443657</v>
+        <v>0.5012792600911206</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5023410041367419</v>
+        <v>0.502580419422116</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5013488947527452</v>
+        <v>0.502580419422116</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5003567853687487</v>
+        <v>0.502580419422116</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5003567853687487</v>
+        <v>0.5019450954068683</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5004264200303735</v>
+        <v>0.5016274333992443</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5004264200303735</v>
+        <v>0.5006744473763727</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4998607306767505</v>
+        <v>0.4999389773990002</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4998607306767505</v>
+        <v>0.500565689353623</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4998607306767505</v>
+        <v>0.500565689353623</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4998607306767505</v>
+        <v>0.500565689353623</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4997910960151257</v>
+        <v>0.500565689353623</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997910960151257</v>
+        <v>0.500565689353623</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4995430686691266</v>
+        <v>0.4995821920302514</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4996127033307514</v>
+        <v>0.4983506673608808</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4996127033307514</v>
+        <v>0.4978546126688825</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4986988406690046</v>
+        <v>0.4974673159996338</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4992254066615027</v>
+        <v>0.5002480273459992</v>
       </c>
     </row>
   </sheetData>
